--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2204.24</v>
+        <v>2212.11</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2243.01</v>
+        <v>2267.41</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4034.01</v>
+        <v>4103.64</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6955.67</v>
+        <v>7075.74</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>21125.63</v>
+        <v>21490.29</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2138.05</v>
+        <v>2134.25</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4687.47</v>
+        <v>4720.55</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4526.07</v>
+        <v>4467.56</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8862.91</v>
+        <v>8748.35</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1039.55</v>
+        <v>1035.19</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6400.01</v>
+        <v>6416.98</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4511.91</v>
+        <v>4523.87</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11094.02</v>
+        <v>11078.46</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4890.15</v>
+        <v>4896.42</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1926.12</v>
+        <v>1936.65</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9573.25</v>
+        <v>9625.6</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1835.99</v>
+        <v>1809.67</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>23794.82</v>
+        <v>23487.29</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>807.3099999999999</v>
+        <v>803.04</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4485.92</v>
+        <v>4462.22</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1115.67</v>
+        <v>1122.98</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3424.87</v>
+        <v>3447.32</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3090.5</v>
+        <v>3132.12</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>34062.77</v>
+        <v>34581.34</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9241.440000000001</v>
+        <v>9466.17</v>
       </c>
     </row>
     <row r="27">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2587.08</v>
+        <v>2652.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>874750-22-CM26</t>
+          <t>707427-5-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>9163.67</v>
+        <v>5941.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3268-16-CM26</t>
+          <t>3268-22-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3913.75</v>
+        <v>3762.07</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3268-22-CM26</t>
+          <t>874750-22-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3651.35</v>
+        <v>9441.540000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>707427-5-CM26</t>
+          <t>3268-16-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5766.76</v>
+        <v>4032.43</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2721.15</v>
+        <v>2728.62</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2529.76</v>
+        <v>2552.77</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1304.08</v>
+        <v>1313.16</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2093.19</v>
+        <v>2107.76</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>8859.08</v>
+        <v>8917.43</v>
       </c>
     </row>
     <row r="37">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12086.36</v>
+        <v>12194.01</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4589-84-CM26</t>
+          <t>3617-30-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1832.75</v>
+        <v>5128.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3617-30-CM26</t>
+          <t>1079445-24-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SECCIÓN COMPRAS XII ZONA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5136.9</v>
+        <v>3376.45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3617-29-CM26</t>
+          <t>1162-22-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3783.92</v>
+        <v>2430.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1162-22-CM26</t>
+          <t>3617-29-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2434.26</v>
+        <v>3777.43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1079445-24-CM26</t>
+          <t>4589-84-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3382.25</v>
+        <v>1829.61</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5544.9</v>
+        <v>5539.18</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>44057.93</v>
+        <v>43993.12</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>34135.78</v>
+        <v>34085.56</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>11531.14</v>
+        <v>11514.17</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>28238.98</v>
+        <v>28085.2</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1523.3</v>
+        <v>1514.33</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2946.27</v>
+        <v>2928.91</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1853.31</v>
+        <v>1842.39</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>6206.35</v>
+        <v>6169.78</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11497.66</v>
+        <v>11453.28</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1728.36</v>
+        <v>1721.69</v>
       </c>
     </row>
     <row r="54">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4654.52</v>
+        <v>4636.55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>935-58-CM26</t>
+          <t>1540-580-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6620.18</v>
+        <v>808.73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1540-580-CM26</t>
+          <t>935-58-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>807.95</v>
+        <v>6626.56</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2030.71</v>
+        <v>2089.7</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3421.68</v>
+        <v>3521.07</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1143.15</v>
+        <v>1176.36</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2091.55</v>
+        <v>2076.79</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6889.1</v>
+        <v>6858.3</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>11812.92</v>
+        <v>11823.1</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2112.19</v>
+        <v>2080.69</v>
       </c>
     </row>
     <row r="64">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1842.02</v>
+        <v>1814.54</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2019-14-CM26</t>
+          <t>1109692-69-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4228.39</v>
+        <v>1093.94</v>
       </c>
     </row>
     <row r="66">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1004.16</v>
+        <v>998.39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1109692-69-CM26</t>
+          <t>2019-14-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1100.26</v>
+        <v>4204.1</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9849.809999999999</v>
+        <v>9707.309999999999</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>924.87</v>
+        <v>900.11</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6763.78</v>
+        <v>6821.18</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1909.49</v>
+        <v>1925.7</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2313.78</v>
+        <v>2333.41</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>797.16</v>
+        <v>806.97</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3277.86</v>
+        <v>3320.64</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2260.11</v>
+        <v>2315.73</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>921.4299999999999</v>
+        <v>929.73</v>
       </c>
     </row>
     <row r="77">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2373.12</v>
+        <v>2382.95</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1057402-4815-CM26</t>
+          <t>4052-54-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1118.69</v>
+        <v>6073.47</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5338-237-CM26</t>
+          <t>1687-15-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1950.8</v>
+        <v>794.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1687-15-CM26</t>
+          <t>5338-237-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>793.26</v>
+        <v>1954.84</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4052-54-CM26</t>
+          <t>1057402-4815-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>6060.91</v>
+        <v>1121.01</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>909.15</v>
+        <v>896.79</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>813.29</v>
+        <v>817.67</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>850.11</v>
+        <v>856.55</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2625.39</v>
+        <v>2650.33</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>51527.74</v>
+        <v>51911.62</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3201.82</v>
+        <v>3225.68</v>
       </c>
     </row>
     <row r="88">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>578.8</v>
+        <v>583.11</v>
       </c>
     </row>
     <row r="89">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3623.58</v>
+        <v>3650.58</v>
       </c>
     </row>
     <row r="90">
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1039.32</v>
+        <v>1028.02</v>
       </c>
     </row>
     <row r="91">
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>18352.18</v>
+        <v>18152.54</v>
       </c>
     </row>
     <row r="92">
@@ -6071,13 +6071,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>912.51</v>
+        <v>915.54</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1609-152-CM26</t>
+          <t>3130-5962-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6117,12 +6117,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6132,13 +6132,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2127.52</v>
+        <v>5466.52</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3130-5962-CM26</t>
+          <t>1609-152-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5437.6</v>
+        <v>2138.84</v>
       </c>
     </row>
     <row r="95">
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>786.13</v>
+        <v>795.35</v>
       </c>
     </row>
     <row r="96">
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2431.05</v>
+        <v>2453.85</v>
       </c>
     </row>
     <row r="97">
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1323.05</v>
+        <v>1332.19</v>
       </c>
     </row>
     <row r="98">
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>9441.440000000001</v>
+        <v>9315.68</v>
       </c>
     </row>
     <row r="99">
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>9531.129999999999</v>
+        <v>9344.57</v>
       </c>
     </row>
     <row r="100">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>5683.73</v>
+        <v>5572.48</v>
       </c>
     </row>
     <row r="101">
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2372.21</v>
+        <v>2381.47</v>
       </c>
     </row>
     <row r="102">
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2659.81</v>
+        <v>2686.56</v>
       </c>
     </row>
     <row r="103">
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4153.82</v>
+        <v>4144.78</v>
       </c>
     </row>
     <row r="104">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3507.49</v>
+        <v>3451.26</v>
       </c>
     </row>
     <row r="105">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1049.69</v>
+        <v>1037.47</v>
       </c>
     </row>
     <row r="106">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2995.14</v>
+        <v>3015.19</v>
       </c>
     </row>
     <row r="107">
@@ -6986,7 +6986,68 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1353.38</v>
+        <v>1362.44</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>707427-46-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>ECOFFICE COMPUTACION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>76.293.503-1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>14497.46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5338-913-CM25</t>
+          <t>697-89-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2212.11</v>
+        <v>2202.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2019-139-CM25</t>
+          <t>935-5732-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>77.338.250-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,28 +630,28 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2267.41</v>
+        <v>5481.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2099-576-CM25</t>
+          <t>3392-115-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.102.137-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4103.64</v>
+        <v>2233.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3130-4198-CM25</t>
+          <t>5338-913-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7075.74</v>
+        <v>2212.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1237328-673-CM25</t>
+          <t>2019-139-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>21490.29</v>
+        <v>2267.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5921-1-CM25</t>
+          <t>2099-576-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2134.25</v>
+        <v>4103.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3268-864-CM25</t>
+          <t>3130-4198-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4720.55</v>
+        <v>7075.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1208985-117-CM25</t>
+          <t>1237328-673-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4467.56</v>
+        <v>21490.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>855-304-CM25</t>
+          <t>5921-1-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8748.35</v>
+        <v>2134.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3617-234-CM25</t>
+          <t>3268-864-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1035.19</v>
+        <v>4720.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3268-924-CM25</t>
+          <t>1208985-117-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6416.98</v>
+        <v>4467.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3268-925-CM25</t>
+          <t>855-304-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4523.87</v>
+        <v>8748.35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1237328-812-CM25</t>
+          <t>3617-234-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11078.46</v>
+        <v>1035.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057402-44653-CM25</t>
+          <t>3268-925-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4896.42</v>
+        <v>4523.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>697-592-CM25</t>
+          <t>3268-924-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1936.65</v>
+        <v>6416.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1057402-44508-CM25</t>
+          <t>1237328-812-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9625.6</v>
+        <v>11078.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1540-11-CM26</t>
+          <t>1057402-44653-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1809.67</v>
+        <v>4896.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5338-7-CM26</t>
+          <t>697-592-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>23487.29</v>
+        <v>1936.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057402-652-CM26</t>
+          <t>1057402-44508-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>803.04</v>
+        <v>9625.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>697-26-CM26</t>
+          <t>1540-11-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4462.22</v>
+        <v>1809.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1057402-874-CM26</t>
+          <t>5338-7-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1122.98</v>
+        <v>23487.29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2983-11-CM26</t>
+          <t>1057402-652-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3447.32</v>
+        <v>803.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3617-3-CM26</t>
+          <t>697-26-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3132.12</v>
+        <v>4462.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>707427-4-CM26</t>
+          <t>2983-11-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>34581.34</v>
+        <v>3447.32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057402-1003-CM26</t>
+          <t>1057402-874-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9466.17</v>
+        <v>1122.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3367-4-CM26</t>
+          <t>3617-3-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.927.400-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2652.48</v>
+        <v>3132.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>707427-5-CM26</t>
+          <t>707427-4-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>77.338.250-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5941.63</v>
+        <v>34581.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3268-22-CM26</t>
+          <t>1057402-1003-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3762.07</v>
+        <v>9466.17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>874750-22-CM26</t>
+          <t>3367-4-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.927.400-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>9441.540000000001</v>
+        <v>2652.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3268-16-CM26</t>
+          <t>874750-22-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4032.43</v>
+        <v>9441.540000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2663-46-CM26</t>
+          <t>3268-16-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2728.62</v>
+        <v>4032.43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3617-22-CM26</t>
+          <t>3268-22-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2552.77</v>
+        <v>3762.07</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1162-26-CM26</t>
+          <t>707427-5-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1313.16</v>
+        <v>5941.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3130-5368-CM26</t>
+          <t>2663-46-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2107.76</v>
+        <v>2728.62</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3166-41-CM26</t>
+          <t>3617-22-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>8917.43</v>
+        <v>2552.77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3166-69-CM26</t>
+          <t>1162-26-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SEBASTIAN PRADO Y COMPANIA LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.085.387-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12194.01</v>
+        <v>1313.16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3617-30-CM26</t>
+          <t>3130-5368-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5128.09</v>
+        <v>2107.76</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1079445-24-CM26</t>
+          <t>3166-41-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3376.45</v>
+        <v>8917.43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1162-22-CM26</t>
+          <t>3166-69-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,22 +2847,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>SEBASTIAN PRADO Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.085.387-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2430.09</v>
+        <v>12194.01</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3617-29-CM26</t>
+          <t>4589-84-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.251.700-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3777.43</v>
+        <v>1829.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4589-84-CM26</t>
+          <t>3617-30-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.251.700-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TORRES DEL PAIN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1829.61</v>
+        <v>5128.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>874750-59-CM26</t>
+          <t>1162-22-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5539.18</v>
+        <v>2430.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3166-78-CM26</t>
+          <t>1079445-24-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>SECCIÓN COMPRAS XII ZONA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>43993.12</v>
+        <v>3376.45</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3166-79-CM26</t>
+          <t>3617-29-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>34085.56</v>
+        <v>3777.43</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3166-80-CM26</t>
+          <t>874750-59-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>11514.17</v>
+        <v>5539.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2348-100-CM26</t>
+          <t>3166-78-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>28085.2</v>
+        <v>43993.12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1162-28-CM26</t>
+          <t>3166-79-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1514.33</v>
+        <v>34085.56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>902977-4-CM26</t>
+          <t>3166-80-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,22 +3396,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2928.91</v>
+        <v>11514.17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1162-32-CM26</t>
+          <t>2348-100-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,22 +3457,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1842.39</v>
+        <v>28085.2</v>
       </c>
     </row>
     <row r="51">
@@ -3564,7 +3564,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1057402-2332-CM26</t>
+          <t>1162-28-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11453.28</v>
+        <v>1514.33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3166-88-CM26</t>
+          <t>902977-4-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,22 +3640,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1721.69</v>
+        <v>2928.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3866-23-CM26</t>
+          <t>1162-32-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4636.55</v>
+        <v>1842.39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1540-580-CM26</t>
+          <t>3166-88-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>808.73</v>
+        <v>1721.69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>935-58-CM26</t>
+          <t>1057402-2332-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>6626.56</v>
+        <v>11453.28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3268-96-CM26</t>
+          <t>3866-23-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,27 +3879,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2089.7</v>
+        <v>4636.55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4305-39-CM26</t>
+          <t>935-58-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3521.07</v>
+        <v>6626.56</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4720-2-CM26</t>
+          <t>1540-580-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1176.36</v>
+        <v>808.73</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3866-35-CM26</t>
+          <t>3268-96-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,22 +4067,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2076.79</v>
+        <v>2089.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1237328-91-CM26</t>
+          <t>4305-39-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6858.3</v>
+        <v>3521.07</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>874750-96-CM26</t>
+          <t>4720-2-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>11823.1</v>
+        <v>1176.36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3268-139-CM26</t>
+          <t>3866-35-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2080.69</v>
+        <v>2076.79</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4305-52-CM26</t>
+          <t>1237328-91-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1814.54</v>
+        <v>6858.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1109692-69-CM26</t>
+          <t>874750-96-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1093.94</v>
+        <v>11823.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1109692-70-CM26</t>
+          <t>3268-139-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>998.39</v>
+        <v>2080.69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2019-14-CM26</t>
+          <t>4305-52-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>4204.1</v>
+        <v>1814.54</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1057402-3473-CM26</t>
+          <t>2019-14-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9707.309999999999</v>
+        <v>4204.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3130-5633-CM26</t>
+          <t>1109692-70-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>900.11</v>
+        <v>998.39</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3268-191-CM26</t>
+          <t>1109692-69-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6821.18</v>
+        <v>1093.94</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3268-192-CM26</t>
+          <t>1057402-3473-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1925.7</v>
+        <v>9707.309999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3130-5672-CM26</t>
+          <t>3130-5633-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2333.41</v>
+        <v>900.11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1540-937-CM26</t>
+          <t>3268-191-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>806.97</v>
+        <v>6821.18</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3241-85-CM26</t>
+          <t>3268-192-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3320.64</v>
+        <v>1925.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3268-216-CM26</t>
+          <t>3130-5672-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2315.73</v>
+        <v>2333.41</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1038-73-CM26</t>
+          <t>1540-937-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>929.73</v>
+        <v>806.97</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3130-5790-CM26</t>
+          <t>3241-85-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.102.028-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2382.95</v>
+        <v>3320.64</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4052-54-CM26</t>
+          <t>3268-216-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>6073.47</v>
+        <v>2315.73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1687-15-CM26</t>
+          <t>1038-73-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>794.9</v>
+        <v>929.73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5338-237-CM26</t>
+          <t>3130-5790-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1954.84</v>
+        <v>2382.95</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1057402-4815-CM26</t>
+          <t>5338-237-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1121.01</v>
+        <v>1954.84</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2663-243-CM26</t>
+          <t>1057402-4815-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,27 +5404,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.250.100-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>896.79</v>
+        <v>1121.01</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1057402-5031-CM26</t>
+          <t>4052-54-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,27 +5465,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>817.67</v>
+        <v>6073.47</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3268-277-CM26</t>
+          <t>1687-15-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>856.55</v>
+        <v>794.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3268-303-CM26</t>
+          <t>2663-243-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,22 +5592,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>69.250.100-4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>ILUSTRE MUNICIPALIDAD DE NATALES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2650.33</v>
+        <v>896.79</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>855-64-CM26</t>
+          <t>1057402-5031-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,22 +5653,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5686,24 +5686,20 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>51911.62</v>
+        <v>817.67</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>709129-15-CM26</t>
+          <t>3268-277-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5718,22 +5714,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ministerio Publico</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5743,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5758,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3225.68</v>
+        <v>856.55</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>855-65-SE26</t>
+          <t>3268-303-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5779,22 +5775,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5812,24 +5808,20 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>583.11</v>
+        <v>2650.33</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>855-66-SE26</t>
+          <t>855-64-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5888,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3650.58</v>
+        <v>51911.62</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1038-100-CM26</t>
+          <t>709129-15-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5909,22 +5901,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ministerio Publico</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5934,12 +5926,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5949,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1028.02</v>
+        <v>3225.68</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1237328-248-CM26</t>
+          <t>855-65-SE26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5970,22 +5962,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5995,28 +5987,32 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>18152.54</v>
+        <v>583.11</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1000813-202-CM26</t>
+          <t>855-66-SE26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6031,22 +6027,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6056,28 +6052,32 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>MARANGUNIC HERMANOS LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>80.586.800-7</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>915.54</v>
+        <v>3650.58</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3130-5962-CM26</t>
+          <t>1038-100-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6117,12 +6117,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6132,13 +6132,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5466.52</v>
+        <v>1028.02</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1609-152-CM26</t>
+          <t>1237328-248-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6193,13 +6193,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2138.84</v>
+        <v>18152.54</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057402-5875-CM26</t>
+          <t>1000813-202-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>MARANGUNIC HERMANOS LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>80.586.800-7</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6254,13 +6254,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>795.35</v>
+        <v>915.54</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>697-167-CM26</t>
+          <t>1609-152-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.605.000-3</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>INSTITUTO ANTARTICO CHILENO</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6300,12 +6300,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2453.85</v>
+        <v>2138.84</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1540-1454-CM26</t>
+          <t>3130-5962-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6376,13 +6376,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1332.19</v>
+        <v>5466.52</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5338-353-CM26</t>
+          <t>1057402-5875-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6437,13 +6437,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>9315.68</v>
+        <v>795.35</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5338-354-CM26</t>
+          <t>697-167-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.605.000-3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>INSTITUTO ANTARTICO CHILENO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6498,13 +6498,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>9344.57</v>
+        <v>2453.85</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5338-355-CM26</t>
+          <t>1540-1454-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6559,13 +6559,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>5572.48</v>
+        <v>1332.19</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1208985-88-CM26</t>
+          <t>5338-353-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>77.338.250-6</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2381.47</v>
+        <v>9315.68</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1208985-89-CM26</t>
+          <t>5338-354-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6681,13 +6681,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2686.56</v>
+        <v>9344.57</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3268-487-CM26</t>
+          <t>5338-355-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6697,27 +6697,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4144.78</v>
+        <v>5572.48</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3268-503-CM26</t>
+          <t>1208985-88-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6763,22 +6763,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6803,13 +6803,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3451.26</v>
+        <v>2381.47</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3263-35-CM26</t>
+          <t>1208985-89-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6824,22 +6824,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>70.788.300-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>CENTRAL ODONTOLOGICA MAGALLANES</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1037.47</v>
+        <v>2686.56</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3241-216-CM26</t>
+          <t>3268-487-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6925,13 +6925,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3015.19</v>
+        <v>4144.78</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3241-217-CM26</t>
+          <t>3268-503-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6986,13 +6986,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1362.44</v>
+        <v>3451.26</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>707427-46-CM26</t>
+          <t>3263-35-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.788.300-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CENTRAL ODONTOLOGICA MAGALLANES</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ECOFFICE COMPUTACION LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.293.503-1</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7047,6 +7047,189 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
+        <v>1037.47</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>3241-217-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>61.102.028-7</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>86.527.400-9</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>1362.44</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>3241-216-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>61.102.028-7</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>3015.19</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>707427-46-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>ECOFFICE COMPUTACION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>76.293.503-1</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
         <v>14497.46</v>
       </c>
     </row>
